--- a/EXAMPLE_URL_TIMMINGS.xlsx
+++ b/EXAMPLE_URL_TIMMINGS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedatwani/Desktop/Personal Projects/UOWD Enrolment Bot python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedatwani/Desktop/Personal Projects/UOWD-Schedular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B63F3811-B585-8E4D-8E2D-FB0A89002AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9E8406-B098-F444-961B-D4C54F59DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16940" xr2:uid="{86FFCDF1-51D2-9D4E-9120-49D675A8CCFD}"/>
   </bookViews>
@@ -44,22 +44,22 @@
     <t>TYPE</t>
   </si>
   <si>
-    <t>COMPUTER LAB</t>
-  </si>
-  <si>
     <t>URL LINK</t>
   </si>
   <si>
     <t>STRING</t>
   </si>
   <si>
-    <t>ISIT312</t>
-  </si>
-  <si>
-    <t>ISIT312Com_Obaid Ulla_Wed10:30</t>
-  </si>
-  <si>
-    <t>https://solss.uow.edu.au/sid/sols_tutorial_enrolment.display_tutorial_timetable?p_sub_inst_id_pri=369133&amp;p_sub_inst_id_ori=369133&amp;p_type_id=10&amp;p_student_number=#######&amp;p_session_id=&amp;p_screen=tut_enrol&amp;p_cs=22737582801266117540</t>
+    <t>https://solss.uow.edu.au/sid/sols_tutorial_enrolment.display_tutorial_timetable?p_sub_inst_id_pri=384559&amp;p_sub_inst_id_ori=384559&amp;p_type_id=2&amp;p_student_number=8485811&amp;p_session_id=&amp;p_screen=tut_enrol&amp;p_cs=18899591242629965670</t>
+  </si>
+  <si>
+    <t>INE301</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tutorial</t>
+  </si>
+  <si>
+    <t>INE 301Tut_Donia AlRaw_Mon12.5</t>
   </si>
 </sst>
 </file>
@@ -465,10 +465,10 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="21" x14ac:dyDescent="0.25">
@@ -476,13 +476,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="21" x14ac:dyDescent="0.25">
@@ -523,7 +523,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" location="######&amp;p_session_id=&amp;p_screen=tut_enrol&amp;p_cs=22737582801266117540" xr:uid="{6B6FBF28-C071-8C40-9B11-4139B1DD0F6E}"/>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{6B6FBF28-C071-8C40-9B11-4139B1DD0F6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
